--- a/etf_holdings/2026-10-06_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-06_00403A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:08</t>
+          <t>2026-10-06 02:27:41</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:08</t>
+          <t>2026-10-06 02:27:41</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:08</t>
+          <t>2026-10-06 02:27:41</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:08</t>
+          <t>2026-10-06 02:27:41</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:08</t>
+          <t>2026-10-06 02:27:41</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:08</t>
+          <t>2026-10-06 02:27:41</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:08</t>
+          <t>2026-10-06 02:27:41</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:08</t>
+          <t>2026-10-06 02:27:41</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:08</t>
+          <t>2026-10-06 02:27:41</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:08</t>
+          <t>2026-10-06 02:27:41</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:08</t>
+          <t>2026-10-06 02:27:41</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:08</t>
+          <t>2026-10-06 02:27:41</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:08</t>
+          <t>2026-10-06 02:27:41</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:08</t>
+          <t>2026-10-06 02:27:41</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:08</t>
+          <t>2026-10-06 02:27:41</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:09</t>
+          <t>2026-10-06 02:27:42</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:09</t>
+          <t>2026-10-06 02:27:42</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:09</t>
+          <t>2026-10-06 02:27:42</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:09</t>
+          <t>2026-10-06 02:27:42</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:09</t>
+          <t>2026-10-06 02:27:42</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:09</t>
+          <t>2026-10-06 02:27:42</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:09</t>
+          <t>2026-10-06 02:27:42</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:09</t>
+          <t>2026-10-06 02:27:42</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:09</t>
+          <t>2026-10-06 02:27:42</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:09</t>
+          <t>2026-10-06 02:27:42</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:09</t>
+          <t>2026-10-06 02:27:42</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:09</t>
+          <t>2026-10-06 02:27:42</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:09</t>
+          <t>2026-10-06 02:27:42</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:09</t>
+          <t>2026-10-06 02:27:42</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:09</t>
+          <t>2026-10-06 02:27:42</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:10</t>
+          <t>2026-10-06 02:27:44</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:10</t>
+          <t>2026-10-06 02:27:44</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:10</t>
+          <t>2026-10-06 02:27:44</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:10</t>
+          <t>2026-10-06 02:27:44</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:10</t>
+          <t>2026-10-06 02:27:44</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:10</t>
+          <t>2026-10-06 02:27:44</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:10</t>
+          <t>2026-10-06 02:27:44</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:10</t>
+          <t>2026-10-06 02:27:44</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:10</t>
+          <t>2026-10-06 02:27:44</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:10</t>
+          <t>2026-10-06 02:27:44</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:10</t>
+          <t>2026-10-06 02:27:44</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:10</t>
+          <t>2026-10-06 02:27:44</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:10</t>
+          <t>2026-10-06 02:27:44</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:10</t>
+          <t>2026-10-06 02:27:44</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:10</t>
+          <t>2026-10-06 02:27:44</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:11</t>
+          <t>2026-10-06 02:27:45</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:11</t>
+          <t>2026-10-06 02:27:45</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:11</t>
+          <t>2026-10-06 02:27:45</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:11</t>
+          <t>2026-10-06 02:27:45</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:11</t>
+          <t>2026-10-06 02:27:45</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-10-06_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-06_00403A_full_holdings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M51"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:41</t>
+          <t>2026-10-06 19:16:39</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+3%2575</t>
+          <t>+0.39%2585</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+3%</t>
+          <t>+0.39%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2575</v>
+        <v>2585</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>13.31%7,700,000</t>
+          <t>13.64%7,700,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>13.31%</t>
+          <t>13.64%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.40%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:41</t>
+          <t>2026-10-06 19:16:39</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -565,38 +565,38 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2454聯發科</t>
+          <t>3037欣興</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+4.34%5165</t>
+          <t>-1.13%1310</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+4.34%</t>
+          <t>-1.13%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5165</v>
+        <v>1310</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7.66%2,210,000</t>
+          <t>7.00%7,800,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>7.66%</t>
+          <t>7.00%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>2210000</v>
+        <v>7800000</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:41</t>
+          <t>2026-10-06 19:16:39</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -626,38 +626,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3037欣興</t>
+          <t>2454聯發科</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+1.53%1325</t>
+          <t>-4.74%4920</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+1.53%</t>
+          <t>-4.74%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1325</v>
+        <v>4920</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7.53%8,460,000</t>
+          <t>6.57%1,950,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>7.53%</t>
+          <t>6.57%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>8460000</v>
+        <v>1950000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:41</t>
+          <t>2026-10-06 19:16:39</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -687,38 +687,38 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3653健策</t>
+          <t>2383台光電</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+5.96%7205</t>
+          <t>+5.18%5995</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+5.96%</t>
+          <t>+5.18%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>7205</v>
+        <v>5995</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.39%1,115,000</t>
+          <t>5.75%1,400,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.39%</t>
+          <t>5.75%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>1115000</v>
+        <v>1400000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.31%</t>
+          <t>+0.28%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:41</t>
+          <t>2026-10-06 19:16:39</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -748,38 +748,38 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2383台光電</t>
+          <t>3653健策</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+9.93%5700</t>
+          <t>-1.73%7080</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+9.93%</t>
+          <t>-1.73%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>5700</v>
+        <v>7080</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5.36%1,400,000</t>
+          <t>5.41%1,115,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.36%</t>
+          <t>5.41%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>1400000</v>
+        <v>1115000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.50%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:41</t>
+          <t>2026-10-06 19:16:39</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+4.22%3585</t>
+          <t>+2.79%3685</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+4.22%</t>
+          <t>+2.79%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>3585</v>
+        <v>3685</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5.06%2,100,000</t>
+          <t>5.30%2,100,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.06%</t>
+          <t>5.30%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.21%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:41</t>
+          <t>2026-10-06 19:16:39</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,25 +875,25 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+6.37%2005</t>
+          <t>+2.24%2050</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+6.37%</t>
+          <t>+2.24%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2005</v>
+        <v>2050</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.90%2,900,000</t>
+          <t>4.07%2,900,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.90%</t>
+          <t>4.07%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.24%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:41</t>
+          <t>2026-10-06 19:16:39</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2303聯電</t>
+          <t>6223旺矽</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-5.57%152.5</t>
+          <t>+2.72%5670</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-5.57%</t>
+          <t>+2.72%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>152.5</v>
+        <v>5670</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.89%38,000,000</t>
+          <t>3.61%930,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.89%</t>
+          <t>3.61%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>38000000</v>
+        <v>930000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:41</t>
+          <t>2026-10-06 19:16:39</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0%626</t>
+          <t>-0.16%625</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.53%8,400,000</t>
+          <t>3.60%8,400,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.53%</t>
+          <t>3.60%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:41</t>
+          <t>2026-10-06 19:16:39</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1053,38 +1053,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>6223旺矽</t>
+          <t>3443創意</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+3.95%5520</t>
+          <t>-2.62%8375</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+3.95%</t>
+          <t>-2.62%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>5520</v>
+        <v>8375</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.45%930,000</t>
+          <t>3.56%620,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.45%</t>
+          <t>3.56%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>930000</v>
+        <v>620000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:41</t>
+          <t>2026-10-06 19:16:39</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3443創意</t>
+          <t>3189景碩</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+8.86%8600</t>
+          <t>-2.28%1070</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+8.86%</t>
+          <t>-2.28%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>8600</v>
+        <v>1070</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.29%570,000</t>
+          <t>3.26%4,450,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.29%</t>
+          <t>3.26%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>570000</v>
+        <v>4450000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.28%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:41</t>
+          <t>2026-10-06 19:16:39</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3189景碩</t>
+          <t>8046南電</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+4.29%1095</t>
+          <t>+0.67%1505</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+4.29%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1095</v>
+        <v>1505</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.27%4,450,000</t>
+          <t>3.10%3,010,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.27%</t>
+          <t>3.10%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>4450000</v>
+        <v>3010000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:41</t>
+          <t>2026-10-06 19:16:39</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>8046南電</t>
+          <t>6669緯穎</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+2.4%1495</t>
+          <t>+6.51%2290</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+2.4%</t>
+          <t>+6.51%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1495</v>
+        <v>2290</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.02%3,010,000</t>
+          <t>2.66%1,697,956</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.02%</t>
+          <t>2.66%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>3010000</v>
+        <v>1697956</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:41</t>
+          <t>2026-10-06 19:16:39</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>6669緯穎</t>
+          <t>2303聯電</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+3.12%2150</t>
+          <t>-3.28%147.5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+3.12%</t>
+          <t>-3.28%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>2150</v>
+        <v>147.5</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.45%1,697,956</t>
+          <t>2.43%24,000,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.45%</t>
+          <t>2.43%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>1697956</v>
+        <v>24000000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:41</t>
+          <t>2026-10-06 19:16:39</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,25 +1363,25 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-2.17%2485</t>
+          <t>-6.44%2325</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-2.17%</t>
+          <t>-6.44%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>2485</v>
+        <v>2325</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.44%1,460,000</t>
+          <t>2.33%1,460,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.44%</t>
+          <t>2.33%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:42</t>
+          <t>2026-10-06 19:16:41</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,38 +1419,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>6488環球晶</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+9.88%1780</t>
+          <t>+2.12%1205</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+9.88%</t>
+          <t>+2.12%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1780</v>
+        <v>1205</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.27%1,900,000</t>
+          <t>2.33%2,824,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.27%</t>
+          <t>2.33%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>1900000</v>
+        <v>2824000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.21%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:42</t>
+          <t>2026-10-06 19:16:41</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>6488環球晶</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-0.84%1180</t>
+          <t>-1.4%1755</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>-1.4%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1180</v>
+        <v>1755</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.24%2,824,000</t>
+          <t>2.28%1,900,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.24%</t>
+          <t>2.28%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>2824000</v>
+        <v>1900000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:42</t>
+          <t>2026-10-06 19:16:41</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1546,25 +1546,25 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+5.6%2075</t>
+          <t>-1.2%2050</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+5.6%</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>2075</v>
+        <v>2050</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.23%1,600,000</t>
+          <t>2.25%1,600,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.23%</t>
+          <t>2.25%</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:42</t>
+          <t>2026-10-06 19:16:41</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>8996高力</t>
+          <t>1303南亞</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+5.63%1595</t>
+          <t>+2.45%293</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+5.63%</t>
+          <t>+2.45%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1595</v>
+        <v>293</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.93%1,800,000</t>
+          <t>2.21%11,000,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.93%</t>
+          <t>2.21%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>1800000</v>
+        <v>11000000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:42</t>
+          <t>2026-10-06 19:16:41</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1303南亞</t>
+          <t>8996高力</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+10%286</t>
+          <t>+0.31%1600</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+10%</t>
+          <t>+0.31%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>286</v>
+        <v>1600</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.92%10,000,000</t>
+          <t>1.97%1,800,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.92%</t>
+          <t>1.97%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>10000000</v>
+        <v>1800000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.18%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:42</t>
+          <t>2026-10-06 19:16:41</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1729,25 +1729,25 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+3.61%19520</t>
+          <t>-2.74%18985</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+3.61%</t>
+          <t>-2.74%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>19520</v>
+        <v>18985</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.25%95,500</t>
+          <t>1.24%95,500</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>1.24%</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:42</t>
+          <t>2026-10-06 19:16:41</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,25 +1790,25 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+0.76%530</t>
+          <t>-0.94%525</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+0.76%</t>
+          <t>-0.94%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.00%2,800,000</t>
+          <t>1.01%2,800,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>1.01%</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:42</t>
+          <t>2026-10-06 19:16:41</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,25 +1851,25 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+7%6730</t>
+          <t>+1.86%6855</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+7%</t>
+          <t>+1.86%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>6730</v>
+        <v>6855</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.90%200,000</t>
+          <t>0.94%200,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.94%</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:42</t>
+          <t>2026-10-06 19:16:41</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1912,25 +1912,25 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-0.51%294</t>
+          <t>+1.36%298</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-0.51%</t>
+          <t>+1.36%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.79%4,000,000</t>
+          <t>0.82%4,000,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>0.82%</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:42</t>
+          <t>2026-10-06 19:16:41</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,16 +1973,16 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+9.96%13355</t>
+          <t>-1.91%13100</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+9.96%</t>
+          <t>-1.91%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>13355</v>
+        <v>13100</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:42</t>
+          <t>2026-10-06 19:16:41</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2034,16 +2034,16 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+6.06%2450</t>
+          <t>-1.43%2415</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+6.06%</t>
+          <t>-1.43%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>2450</v>
+        <v>2415</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:42</t>
+          <t>2026-10-06 19:16:41</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,38 +2090,38 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>3450聯鈞</t>
+          <t>2317鴻海</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+0.92%548</t>
+          <t>+0.79%256</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+0.92%</t>
+          <t>+0.79%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>548</v>
+        <v>256</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.55%1,500,000</t>
+          <t>0.56%3,200,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.55%</t>
+          <t>0.56%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>1500000</v>
+        <v>3200000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:42</t>
+          <t>2026-10-06 19:16:41</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,25 +2151,25 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2317鴻海</t>
+          <t>3450聯鈞</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+1.2%254</t>
+          <t>-3.1%531</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+1.2%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>254</v>
+        <v>531</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.55%3,200,000</t>
+          <t>0.55%1,500,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2178,11 +2178,11 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>3200000</v>
+        <v>1500000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:42</t>
+          <t>2026-10-06 19:16:41</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,16 +2217,16 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+0.5%399</t>
+          <t>-1%395</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+0.5%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:42</t>
+          <t>2026-10-06 19:16:41</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,38 +2273,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>6442光聖</t>
+          <t>3583辛耘</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+4.92%1705</t>
+          <t>+2.42%762</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+4.92%</t>
+          <t>+2.42%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1705</v>
+        <v>762</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.40%350,000</t>
+          <t>0.42%800,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.42%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>350000</v>
+        <v>800000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:44</t>
+          <t>2026-10-06 19:16:42</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,25 +2334,25 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>3583辛耘</t>
+          <t>6442光聖</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+3.19%744</t>
+          <t>-3.23%1650</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+3.19%</t>
+          <t>-3.23%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>744</v>
+        <v>1650</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.40%800,000</t>
+          <t>0.40%350,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2361,11 +2361,11 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>800000</v>
+        <v>350000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:44</t>
+          <t>2026-10-06 19:16:42</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2400,25 +2400,25 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0%111.5</t>
+          <t>+0.45%112</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+0.45%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>111.5</v>
+        <v>112</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.30%4,000,000</t>
+          <t>0.31%4,000,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.31%</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:44</t>
+          <t>2026-10-06 19:16:42</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,34 +2456,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2481強茂</t>
+          <t>2368金像電</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+3.44%180.5</t>
+          <t>+3.7%1260</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+3.44%</t>
+          <t>+3.7%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>180.5</v>
+        <v>1260</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.16%1,300,000</t>
+          <t>0.17%200,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.16%</t>
+          <t>0.17%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>1300000</v>
+        <v>200000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:44</t>
+          <t>2026-10-06 19:16:42</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,38 +2517,38 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1560中砂</t>
+          <t>2481強茂</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+2.46%1040</t>
+          <t>-2.49%176</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+2.46%</t>
+          <t>-2.49%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1040</v>
+        <v>176</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.13%191,000</t>
+          <t>0.16%1,300,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.13%</t>
+          <t>0.16%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>191000</v>
+        <v>1300000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:44</t>
+          <t>2026-10-06 19:16:42</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,38 +2578,38 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2455全新</t>
+          <t>1560中砂</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+4.48%606</t>
+          <t>-0.96%1030</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+4.48%</t>
+          <t>-0.96%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>606</v>
+        <v>1030</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.12%300,000</t>
+          <t>0.13%191,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.12%</t>
+          <t>0.13%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>300000</v>
+        <v>191000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:44</t>
+          <t>2026-10-06 19:16:42</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,38 +2639,38 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>6285啟碁</t>
+          <t>2455全新</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+4.83%249.5</t>
+          <t>-6.44%567</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+4.83%</t>
+          <t>-6.44%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>249.5</v>
+        <v>567</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.06%350,000</t>
+          <t>0.08%200,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.06%</t>
+          <t>0.08%</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>350000</v>
+        <v>200000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:44</t>
+          <t>2026-10-06 19:16:42</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2700,25 +2700,25 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2301光寶科</t>
+          <t>6285啟碁</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+5.86%298</t>
+          <t>+2.61%256</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+5.86%</t>
+          <t>+2.61%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>298</v>
+        <v>256</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.06%300,000</t>
+          <t>0.06%350,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2727,7 +2727,7 @@
         </is>
       </c>
       <c r="K38" t="n">
-        <v>300000</v>
+        <v>350000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:44</t>
+          <t>2026-10-06 19:16:42</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1717長興</t>
+          <t>2301光寶科</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+0.54%74.6</t>
+          <t>+0.34%299</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+0.54%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>74.59999999999999</v>
+        <v>299</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.05%900,000</t>
+          <t>0.06%300,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>0.06%</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>900000</v>
+        <v>300000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:44</t>
+          <t>2026-10-06 19:16:42</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,34 +2822,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>8358金居</t>
+          <t>1717長興</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+9.83%570</t>
+          <t>+0.4%74.9</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+9.83%</t>
+          <t>+0.4%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>570</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.02%50,000</t>
+          <t>0.05%900,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.02%</t>
+          <t>0.05%</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>50000</v>
+        <v>900000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:44</t>
+          <t>2026-10-06 19:16:42</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2883,38 +2883,38 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>3264欣銓</t>
+          <t>8358金居</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-1.43%241.5</t>
+          <t>-3.33%551</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-1.43%</t>
+          <t>-3.33%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>241.5</v>
+        <v>551</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0%1,000</t>
+          <t>0.02%50,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.02%</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>1000</v>
+        <v>50000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:44</t>
+          <t>2026-10-06 19:16:42</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2944,21 +2944,21 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2337旺宏</t>
+          <t>3264欣銓</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-0.41%121.5</t>
+          <t>+1.86%246</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>+1.86%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>121.5</v>
+        <v>246</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:44</t>
+          <t>2026-10-06 19:16:42</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3005,21 +3005,21 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>8299群聯</t>
+          <t>2337旺宏</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+0.24%2100</t>
+          <t>-1.65%119.5</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+0.24%</t>
+          <t>-1.65%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>2100</v>
+        <v>119.5</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:44</t>
+          <t>2026-10-06 19:16:42</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3066,21 +3066,21 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>6196帆宣</t>
+          <t>8299群聯</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>+9.87%679</t>
+          <t>-0.48%2090</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+9.87%</t>
+          <t>-0.48%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>679</v>
+        <v>2090</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:44</t>
+          <t>2026-10-06 19:16:42</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3127,21 +3127,21 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>6239力成</t>
+          <t>6196帆宣</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-3.41%297.5</t>
+          <t>-2.36%663</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-3.41%</t>
+          <t>-2.36%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>297.5</v>
+        <v>663</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:44</t>
+          <t>2026-10-06 19:16:42</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3188,21 +3188,21 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2049上銀</t>
+          <t>6239力成</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>+3.91%345.5</t>
+          <t>+4.37%310.5</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>+3.91%</t>
+          <t>+4.37%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>345.5</v>
+        <v>310.5</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:45</t>
+          <t>2026-10-06 19:16:43</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3249,21 +3249,21 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2360致茂</t>
+          <t>2049上銀</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>+6.16%2325</t>
+          <t>-1.74%339.5</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+6.16%</t>
+          <t>-1.74%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>2325</v>
+        <v>339.5</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:45</t>
+          <t>2026-10-06 19:16:43</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3310,21 +3310,21 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2404漢唐</t>
+          <t>2360致茂</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>+1.95%1310</t>
+          <t>+1.08%2350</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+1.95%</t>
+          <t>+1.08%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>1310</v>
+        <v>2350</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:45</t>
+          <t>2026-10-06 19:16:43</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3371,21 +3371,21 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>7769鴻勁</t>
+          <t>2404漢唐</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>+4.21%5815</t>
+          <t>+1.91%1335</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>+4.21%</t>
+          <t>+1.91%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>5815</v>
+        <v>1335</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:45</t>
+          <t>2026-10-06 19:16:43</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3432,21 +3432,21 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2344華邦電</t>
+          <t>7769鴻勁</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>+1.12%181</t>
+          <t>+1.55%5905</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>+1.12%</t>
+          <t>+1.55%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>181</v>
+        <v>5905</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:45</t>
+          <t>2026-10-06 19:16:43</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3493,21 +3493,21 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>3711日月光投控</t>
+          <t>2344華邦電</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>+4.07%742</t>
+          <t>-1.93%177.5</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>+4.07%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>742</v>
+        <v>177.5</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3528,6 +3528,67 @@
         </is>
       </c>
       <c r="M51" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-10-06 19:16:43</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>4</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>3711日月光投控</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>+0.27%744</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>+0.27%</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>744</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0%1,000</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
         <is>
           <t>登入查看</t>
         </is>

--- a/etf_holdings/2026-10-06_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-06_00403A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:39</t>
+          <t>2026-10-06 23:19:21</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:39</t>
+          <t>2026-10-06 23:19:21</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:39</t>
+          <t>2026-10-06 23:19:21</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:39</t>
+          <t>2026-10-06 23:19:21</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:39</t>
+          <t>2026-10-06 23:19:21</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:39</t>
+          <t>2026-10-06 23:19:21</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:39</t>
+          <t>2026-10-06 23:19:21</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:39</t>
+          <t>2026-10-06 23:19:21</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:39</t>
+          <t>2026-10-06 23:19:21</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:39</t>
+          <t>2026-10-06 23:19:21</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:39</t>
+          <t>2026-10-06 23:19:21</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:39</t>
+          <t>2026-10-06 23:19:21</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:39</t>
+          <t>2026-10-06 23:19:21</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:39</t>
+          <t>2026-10-06 23:19:21</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:39</t>
+          <t>2026-10-06 23:19:21</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:41</t>
+          <t>2026-10-06 23:19:22</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:41</t>
+          <t>2026-10-06 23:19:22</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:41</t>
+          <t>2026-10-06 23:19:22</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:41</t>
+          <t>2026-10-06 23:19:22</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:41</t>
+          <t>2026-10-06 23:19:22</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:41</t>
+          <t>2026-10-06 23:19:22</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:41</t>
+          <t>2026-10-06 23:19:22</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:41</t>
+          <t>2026-10-06 23:19:22</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:41</t>
+          <t>2026-10-06 23:19:22</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:41</t>
+          <t>2026-10-06 23:19:22</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:41</t>
+          <t>2026-10-06 23:19:22</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:41</t>
+          <t>2026-10-06 23:19:22</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:41</t>
+          <t>2026-10-06 23:19:22</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:41</t>
+          <t>2026-10-06 23:19:22</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:41</t>
+          <t>2026-10-06 23:19:22</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:42</t>
+          <t>2026-10-06 23:19:24</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:42</t>
+          <t>2026-10-06 23:19:24</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:42</t>
+          <t>2026-10-06 23:19:24</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:42</t>
+          <t>2026-10-06 23:19:24</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:42</t>
+          <t>2026-10-06 23:19:24</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:42</t>
+          <t>2026-10-06 23:19:24</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:42</t>
+          <t>2026-10-06 23:19:24</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:42</t>
+          <t>2026-10-06 23:19:24</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:42</t>
+          <t>2026-10-06 23:19:24</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:42</t>
+          <t>2026-10-06 23:19:24</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:42</t>
+          <t>2026-10-06 23:19:24</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:42</t>
+          <t>2026-10-06 23:19:24</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:42</t>
+          <t>2026-10-06 23:19:24</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:42</t>
+          <t>2026-10-06 23:19:24</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:42</t>
+          <t>2026-10-06 23:19:24</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:43</t>
+          <t>2026-10-06 23:19:25</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:43</t>
+          <t>2026-10-06 23:19:25</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:43</t>
+          <t>2026-10-06 23:19:25</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:43</t>
+          <t>2026-10-06 23:19:25</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:43</t>
+          <t>2026-10-06 23:19:25</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:43</t>
+          <t>2026-10-06 23:19:25</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">

--- a/etf_holdings/2026-10-06_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-06_00403A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:21</t>
+          <t>2026-10-06 23:27:51</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:21</t>
+          <t>2026-10-06 23:27:51</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:21</t>
+          <t>2026-10-06 23:27:51</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:21</t>
+          <t>2026-10-06 23:27:51</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:21</t>
+          <t>2026-10-06 23:27:51</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:21</t>
+          <t>2026-10-06 23:27:51</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:21</t>
+          <t>2026-10-06 23:27:51</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:21</t>
+          <t>2026-10-06 23:27:51</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:21</t>
+          <t>2026-10-06 23:27:51</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:21</t>
+          <t>2026-10-06 23:27:51</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:21</t>
+          <t>2026-10-06 23:27:51</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:21</t>
+          <t>2026-10-06 23:27:51</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:21</t>
+          <t>2026-10-06 23:27:51</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:21</t>
+          <t>2026-10-06 23:27:51</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:21</t>
+          <t>2026-10-06 23:27:51</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:22</t>
+          <t>2026-10-06 23:27:52</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:22</t>
+          <t>2026-10-06 23:27:52</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:22</t>
+          <t>2026-10-06 23:27:52</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:22</t>
+          <t>2026-10-06 23:27:52</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:22</t>
+          <t>2026-10-06 23:27:52</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:22</t>
+          <t>2026-10-06 23:27:52</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:22</t>
+          <t>2026-10-06 23:27:52</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:22</t>
+          <t>2026-10-06 23:27:52</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:22</t>
+          <t>2026-10-06 23:27:52</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:22</t>
+          <t>2026-10-06 23:27:52</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:22</t>
+          <t>2026-10-06 23:27:52</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:22</t>
+          <t>2026-10-06 23:27:52</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:22</t>
+          <t>2026-10-06 23:27:52</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:22</t>
+          <t>2026-10-06 23:27:52</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:22</t>
+          <t>2026-10-06 23:27:52</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:24</t>
+          <t>2026-10-06 23:27:53</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:24</t>
+          <t>2026-10-06 23:27:53</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:24</t>
+          <t>2026-10-06 23:27:53</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:24</t>
+          <t>2026-10-06 23:27:53</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:24</t>
+          <t>2026-10-06 23:27:53</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:24</t>
+          <t>2026-10-06 23:27:53</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:24</t>
+          <t>2026-10-06 23:27:53</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:24</t>
+          <t>2026-10-06 23:27:53</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:24</t>
+          <t>2026-10-06 23:27:53</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:24</t>
+          <t>2026-10-06 23:27:53</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:24</t>
+          <t>2026-10-06 23:27:53</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:24</t>
+          <t>2026-10-06 23:27:53</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:24</t>
+          <t>2026-10-06 23:27:53</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:24</t>
+          <t>2026-10-06 23:27:53</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:24</t>
+          <t>2026-10-06 23:27:53</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:25</t>
+          <t>2026-10-06 23:27:54</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:25</t>
+          <t>2026-10-06 23:27:54</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:25</t>
+          <t>2026-10-06 23:27:54</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:25</t>
+          <t>2026-10-06 23:27:54</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:25</t>
+          <t>2026-10-06 23:27:54</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:25</t>
+          <t>2026-10-06 23:27:54</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">

--- a/etf_holdings/2026-10-06_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-06_00403A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:51</t>
+          <t>2026-10-06 23:58:24</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:51</t>
+          <t>2026-10-06 23:58:24</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:51</t>
+          <t>2026-10-06 23:58:24</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:51</t>
+          <t>2026-10-06 23:58:24</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:51</t>
+          <t>2026-10-06 23:58:24</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:51</t>
+          <t>2026-10-06 23:58:24</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:51</t>
+          <t>2026-10-06 23:58:24</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:51</t>
+          <t>2026-10-06 23:58:24</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:51</t>
+          <t>2026-10-06 23:58:24</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:51</t>
+          <t>2026-10-06 23:58:24</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:51</t>
+          <t>2026-10-06 23:58:24</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:51</t>
+          <t>2026-10-06 23:58:24</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:51</t>
+          <t>2026-10-06 23:58:24</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:51</t>
+          <t>2026-10-06 23:58:24</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:51</t>
+          <t>2026-10-06 23:58:24</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:52</t>
+          <t>2026-10-06 23:58:25</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:52</t>
+          <t>2026-10-06 23:58:25</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:52</t>
+          <t>2026-10-06 23:58:25</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:52</t>
+          <t>2026-10-06 23:58:25</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:52</t>
+          <t>2026-10-06 23:58:25</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:52</t>
+          <t>2026-10-06 23:58:25</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:52</t>
+          <t>2026-10-06 23:58:25</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:52</t>
+          <t>2026-10-06 23:58:25</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:52</t>
+          <t>2026-10-06 23:58:25</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:52</t>
+          <t>2026-10-06 23:58:25</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:52</t>
+          <t>2026-10-06 23:58:25</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:52</t>
+          <t>2026-10-06 23:58:25</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:52</t>
+          <t>2026-10-06 23:58:25</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:52</t>
+          <t>2026-10-06 23:58:25</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:52</t>
+          <t>2026-10-06 23:58:25</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:53</t>
+          <t>2026-10-06 23:58:26</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:53</t>
+          <t>2026-10-06 23:58:26</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:53</t>
+          <t>2026-10-06 23:58:26</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:53</t>
+          <t>2026-10-06 23:58:26</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:53</t>
+          <t>2026-10-06 23:58:26</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:53</t>
+          <t>2026-10-06 23:58:26</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:53</t>
+          <t>2026-10-06 23:58:26</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:53</t>
+          <t>2026-10-06 23:58:26</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:53</t>
+          <t>2026-10-06 23:58:26</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:53</t>
+          <t>2026-10-06 23:58:26</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:53</t>
+          <t>2026-10-06 23:58:26</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:53</t>
+          <t>2026-10-06 23:58:26</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:53</t>
+          <t>2026-10-06 23:58:26</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:53</t>
+          <t>2026-10-06 23:58:26</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:53</t>
+          <t>2026-10-06 23:58:26</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:54</t>
+          <t>2026-10-06 23:58:27</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:54</t>
+          <t>2026-10-06 23:58:27</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:54</t>
+          <t>2026-10-06 23:58:27</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:54</t>
+          <t>2026-10-06 23:58:27</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:54</t>
+          <t>2026-10-06 23:58:27</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:54</t>
+          <t>2026-10-06 23:58:27</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
